--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/MINNESOTA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/MINNESOTA_2012.xlsx
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C134">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C522">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C577">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C865">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C956">
